--- a/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maman et Cécile vont au port. Cécile tient la main de maman. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait touc touc. L'eau clapote. Maman dit : c'est un bateau. C'est le nom du véhicule. Cécile répète : un bateau. Elles restent près. Cécile s'assoit sur le banc. Le bateau glisse. Cécile entend le bruit. Dans le ciel, un avion passe. L'avion fait un grand trait blanc. Maman dit : c'est un avion. C'est un autre nom de véhicule. Cécile dit : un avion. Plus loin, un train roule. Le train fait tchou tchou. Maman dit : c'est un train. Cécile dit : un train. Train, avion, bateau. Cécile nomme. Elle reste avec un adulte.</t>
+          <t>Maman et Cécile vont au port. Cécile tient la main de maman. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait touc touc. L'eau clapote. C'est un bateau. C'est le nom du véhicule. Cécile répète : un bateau. Elles restent près. Cécile s'assoit sur le banc. Le bateau glisse. Cécile entend le bruit. Dans le ciel, un avion passe. L'avion fait un grand trait blanc. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, un train roule. Le train fait tchou tchou. C'est un train. Un train. Train, avion, bateau. Cécile nomme. Elle reste avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maman et Cécile vont au port. Cécile tient la main de maman. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait touc touc. L'eau clapote.
+maman|C'est un bateau. C'est le nom du véhicule.
+narrateur|Cécile répète : un bateau. Elles restent près. Cécile s'assoit sur le banc. Le bateau glisse. Cécile entend le bruit. Dans le ciel, un avion passe. L'avion fait un grand trait blanc.
+maman|C'est un avion. C'est un autre nom de véhicule.
+enfant-f|Un avion. Plus loin, un train roule.
+narrateur|Le train fait tchou tchou.
+maman|C'est un train.
+enfant-f|Un train. Train, avion, bateau.
+narrateur|Cécile nomme. Elle reste avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile nomme un véhicule. Lequel ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile donne la main à maman. Elles quittent le port.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Cécile nomme. Elle reste avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Cécile nomme un véhicule. Lequel ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Cécile a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Cécile donne la main à maman. Elles quittent le port.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bateau de Cécile</t>
+          <t>Le vent du bac</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut traverser le fleuve en bac. Le vent pousse. Il reste près de maman. L'autre rive arrive.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maman et Cécile vont au port. Cécile tient la main de maman. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait touc touc. L'eau clapote. C'est un bateau. C'est le nom du véhicule. Cécile répète : un bateau. Elles restent près. Cécile s'assoit sur le banc. Le bateau glisse. Cécile entend le bruit. Dans le ciel, un avion passe. L'avion fait un grand trait blanc. C'est un avion. C'est un autre nom de véhicule. Un avion. Plus loin, un train roule. Le train fait tchou tchou. C'est un train. Un train. Train, avion, bateau. Cécile nomme. Elle reste avec un adulte.</t>
+          <t>Le sel du bac pique la lèvre. Une corde épaisse sent le goudron. L'eau clapote contre le quai. Une mouette crie, toute blanche. Nino vit ici, avec maman. Tu as goûté le sel ? Ça pique. Oui. Le bac arrive. En ce moment, le ponton vibre. Le bateau se colle au quai. C'est un bateau ? Oui. C'est le nom du véhicule. Un bateau. On reste avec un adulte. Ils montent avec maman. Nino se tient près d'elle. Le vent tire le manteau. Le bac part tout doux. Ça bouge ! Oui. Tu restes près de moi ? Oui, maman. Le vent devient plus fort. Le capuchon de Nino saute. Mon capuchon ! Tu restes près. Maman le remet. Nino reste contre maman. Le capuchon revient sur la tête. L'eau fait des petits blancs. Tu restes près ? Oui, maman. Le manteau claque encore. Nino serre le tissu de maman. Une goutte d'eau saute sur le pont. L'eau saute. Oui. Nous, on reste ici. Le capuchon tient, cette fois. Le sel pique encore la lèvre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman et Cécile vont au port. Cécile tient la main de maman. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait touc touc. L'eau clapote. Maman dit : c'est un bateau. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Cécile répète : un bateau. Elles restent près. Cécile s'assoit sur le banc. Le bateau glisse. Cécile entend le bruit. Dans le ciel, un avion passe. L'avion fait un grand trait blanc. Maman dit : c'est un avion. C'est un autre nom de véhicule. Cécile dit : un avion. Plus loin, un train roule. Le train fait tchou tchou. Maman dit : c'est un train. Cécile dit : un train. Train, avion, bateau. Cécile nomme. Elle reste avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sel du bac pique la lèvre. Une corde épaisse sent le goudron. L'eau clapote contre le quai. Une mouette crie, toute blanche. Nino vit ici, avec maman. Tu as goûté le sel ? Ça pique. Oui. Le bac arrive. En ce moment, le ponton vibre. Le bateau se colle au quai. C'est un bateau ? Oui. C'est le nom du véhicule. Un bateau. On reste avec un adulte. Ils montent avec maman. Nino se tient près d'elle. Le vent tire le manteau. Le bac part tout doux. Ça bouge ! Oui. Tu restes près de moi ? Oui, maman. Le vent devient plus fort. Le capuchon de Nino saute. Mon capuchon ! Tu restes près. Maman le remet. Nino reste contre maman. Le capuchon revient sur la tête. L'eau fait des petits blancs. Tu restes près ? Oui, maman. Le manteau claque encore. Nino serre le tissu de maman. Une goutte d'eau saute sur le pont. L'eau saute. Oui. Nous, on reste ici. Le capuchon tient, cette fois. Le sel pique encore la lèvre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,18 +1324,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maman et Cécile vont au port. Cécile tient la main de maman. Elles restent avec un adulte. Maman, c'est l'adulte. Un bateau arrive. Le bateau fait touc touc. L'eau clapote.
-maman|C'est un bateau. C'est le nom du véhicule.
-narrateur|Cécile répète : un bateau. Elles restent près. Cécile s'assoit sur le banc. Le bateau glisse. Cécile entend le bruit. Dans le ciel, un avion passe. L'avion fait un grand trait blanc.
-maman|C'est un avion. C'est un autre nom de véhicule.
-enfant-f|Un avion. Plus loin, un train roule.
-narrateur|Le train fait tchou tchou.
-maman|C'est un train.
-enfant-f|Un train. Train, avion, bateau.
-narrateur|Cécile nomme. Elle reste avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le sel du bac pique la lèvre.
+narrateur|Une corde épaisse sent le goudron.
+narrateur|L'eau clapote contre le quai.
+narrateur|Une mouette crie, toute blanche.
+narrateur|Nino vit ici, avec maman.
+maman|Tu as goûté le sel ?
+enfant-m|Ça pique.
+maman|Oui.
+maman|Le bac arrive.
+narrateur|En ce moment, le ponton vibre.
+narrateur|Le bateau se colle au quai.
+enfant-m|C'est un bateau ?
+maman|Oui.
+maman|C'est le nom du véhicule.
+enfant-m|Un bateau.
+maman|On reste avec un adulte.
+narrateur|Ils montent avec maman.
+narrateur|Nino se tient près d'elle.
+narrateur|Le vent tire le manteau.
+narrateur|Le bac part tout doux.
+enfant-m|Ça bouge !
+maman|Oui.
+maman|Tu restes près de moi ?
+enfant-m|Oui, maman.
+narrateur|Le vent devient plus fort.
+narrateur|Le capuchon de Nino saute.
+enfant-m|Mon capuchon !
+maman|Tu restes près.
+maman|Maman le remet.
+narrateur|Nino reste contre maman.
+narrateur|Le capuchon revient sur la tête.
+narrateur|L'eau fait des petits blancs.
+maman|Tu restes près ?
+enfant-m|Oui, maman.
+narrateur|Le manteau claque encore.
+narrateur|Nino serre le tissu de maman.
+narrateur|Une goutte d'eau saute sur le pont.
+enfant-m|L'eau saute.
+maman|Oui.
+maman|Nous, on reste ici.
+narrateur|Le capuchon tient, cette fois.
+narrateur|Le sel pique encore la lèvre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,12 +1392,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cécile nomme un véhicule. Lequel ?</t>
+          <t>Nino nomme le véhicule. Lequel ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un véhicule. Lequel ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino nomme le véhicule. Lequel ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1368,7 +1412,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>bateau | avion | train | un bateau | le bateau</t>
+          <t>bateau | un bateau | le bateau | le bac | avion | train</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle a vu un bateau. Quel véhicule ?</t>
+          <t>Il a pris le bac. Quel véhicule ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1476,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1552,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Cécile nomme un véhicule. Lequel ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino nomme le véhicule.
+narrateur|Lequel ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cécile a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
+          <t>Le vent pousse encore. Nino serre la main de maman. Tu es resté près. Bravo. Le sel pique encore. Oui. Dans le ciel, un trait blanc. Tu vois ça ? Un avion. Oui. C'est un avion. Sur l'autre rive, des rails. Un train file, tout petit. Et ça ? Un train. Nino reste près de maman. Le manteau claque, puis se calme. L'eau devient plus lisse. Tu as encore froid ? Un peu. Maman rentre le col du manteau. Nino reste collé contre elle. Le bac avance tout droit. L'autre rive grandit. Oui. On reste près jusqu'au quai. Une mouette suit le bac. Ses ailes sont bien ouvertes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; du véhicule. Bateau. Avion. Train. Elle est restée avec maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le vent pousse encore. Nino serre la main de maman. Tu es resté près. Bravo. Le sel pique encore. Oui. Dans le ciel, un trait blanc. Tu vois ça ? Un avion. Oui. C'est un avion. Sur l'autre rive, des rails. Un train file, tout petit. Et ça ? Un train. Nino reste près de maman. Le manteau claque, puis se calme. L'eau devient plus lisse. Tu as encore froid ? Un peu. Maman rentre le col du manteau. Nino reste collé contre elle. Le bac avance tout droit. L'autre rive grandit. Oui. On reste près jusqu'au quai. Une mouette suit le bac. Ses ailes sont bien ouvertes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,14 +1641,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1724,36 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Cécile a dit le nom du véhicule. Bateau. Avion. Train. Elle est restée avec maman.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le vent pousse encore.
+narrateur|Nino serre la main de maman.
+maman|Tu es resté près.
+maman|Bravo.
+enfant-m|Le sel pique encore.
+maman|Oui.
+narrateur|Dans le ciel, un trait blanc.
+maman|Tu vois ça ?
+enfant-m|Un avion.
+maman|Oui.
+maman|C'est un avion.
+narrateur|Sur l'autre rive, des rails.
+narrateur|Un train file, tout petit.
+maman|Et ça ?
+enfant-m|Un train.
+narrateur|Nino reste près de maman.
+narrateur|Le manteau claque, puis se calme.
+narrateur|L'eau devient plus lisse.
+maman|Tu as encore froid ?
+enfant-m|Un peu.
+narrateur|Maman rentre le col du manteau.
+narrateur|Nino reste collé contre elle.
+narrateur|Le bac avance tout droit.
+enfant-m|L'autre rive grandit.
+maman|Oui.
+maman|On reste près jusqu'au quai.
+narrateur|Une mouette suit le bac.
+narrateur|Ses ailes sont bien ouvertes.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cécile donne la main à maman. Elles quittent le port.</t>
+          <t>L'autre rive se rapproche. Les arbres deviennent grands. On arrive. On reste près encore. D'accord. Le bac se colle au quai. Maintenant on descend. Ils descendent ensemble. Nino donne la main à maman. Tu es resté près. Le vent était fort. Le quai est mouillé et sombre. Une flaque tremble encore. Tu as les pieds au sec ? Oui. Nino marche près de maman. Le capuchon reste sur sa tête.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à maman. Elles quittent le port.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'autre rive se rapproche. Les arbres deviennent grands. On arrive. On reste près encore. D'accord. Le bac se colle au quai. Maintenant on descend. Ils descendent ensemble. Nino donne la main à maman. Tu es resté près. Le vent était fort. Le quai est mouillé et sombre. Une flaque tremble encore. Tu as les pieds au sec ? Oui. Nino marche près de maman. Le capuchon reste sur sa tête.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,14 +1839,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1918,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Cécile donne la main à maman. Elles quittent le port.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|L'autre rive se rapproche.
+narrateur|Les arbres deviennent grands.
+maman|On arrive.
+maman|On reste près encore.
+enfant-m|D'accord.
+narrateur|Le bac se colle au quai.
+maman|Maintenant on descend.
+narrateur|Ils descendent ensemble.
+narrateur|Nino donne la main à maman.
+maman|Tu es resté près.
+enfant-m|Le vent était fort.
+narrateur|Le quai est mouillé et sombre.
+narrateur|Une flaque tremble encore.
+maman|Tu as les pieds au sec ?
+enfant-m|Oui.
+narrateur|Nino marche près de maman.
+narrateur|Le capuchon reste sur sa tête.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sur le quai, le sel reste aux lèvres. On a traversé. Oui. La corde sent encore le goudron. Une mouette crie, plus loin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le quai, le sel reste aux lèvres. On a traversé. Oui. La corde sent encore le goudron. Une mouette crie, plus loin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +2022,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sur le quai, le sel reste aux lèvres.
+enfant-m|On a traversé.
+maman|Oui.
+narrateur|La corde sent encore le goudron.
+narrateur|Une mouette crie, plus loin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>port et rivière</t>
+          <t>port puis bac, vent d'ouest</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cécile, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
